--- a/Team-Data/2012-13/4-12-2012-13.xlsx
+++ b/Team-Data/2012-13/4-12-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>0.55</v>
+        <v>0.544</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
         <v>80.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L2" t="n">
         <v>8.699999999999999</v>
@@ -691,25 +758,25 @@
         <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O2" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
         <v>19.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.712</v>
+        <v>0.713</v>
       </c>
       <c r="R2" t="n">
         <v>9.1</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U2" t="n">
         <v>24.6</v>
@@ -718,7 +785,7 @@
         <v>14.9</v>
       </c>
       <c r="W2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -727,28 +794,28 @@
         <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
         <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
@@ -757,13 +824,13 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
@@ -784,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>25</v>
@@ -799,7 +866,7 @@
         <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
@@ -861,7 +928,7 @@
         <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.463</v>
@@ -870,31 +937,31 @@
         <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O3" t="n">
         <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R3" t="n">
         <v>8.1</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
         <v>39.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V3" t="n">
         <v>14.6</v>
@@ -903,7 +970,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -912,22 +979,22 @@
         <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
         <v>16</v>
@@ -951,16 +1018,16 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
         <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -981,13 +1048,13 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1092,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
         <v>79.59999999999999</v>
@@ -1049,13 +1116,13 @@
         <v>0.449</v>
       </c>
       <c r="L4" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
         <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O4" t="n">
         <v>17.6</v>
@@ -1064,13 +1131,13 @@
         <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R4" t="n">
         <v>12.7</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T4" t="n">
         <v>42.9</v>
@@ -1082,7 +1149,7 @@
         <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,19 +1158,19 @@
         <v>4.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA4" t="n">
         <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1124,16 +1191,16 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM4" t="n">
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
@@ -1148,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1160,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>17</v>
@@ -1175,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1274,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" t="n">
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>0.228</v>
+        <v>0.231</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J5" t="n">
         <v>81.3</v>
@@ -1234,37 +1301,37 @@
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="O5" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0.749</v>
       </c>
       <c r="R5" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S5" t="n">
         <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U5" t="n">
         <v>19</v>
       </c>
       <c r="V5" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X5" t="n">
         <v>5.9</v>
@@ -1282,10 +1349,10 @@
         <v>93.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.9</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1312,7 +1379,7 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>27</v>
@@ -1339,10 +1406,10 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1357,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
         <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.544</v>
+        <v>0.551</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,7 +1474,7 @@
         <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.436</v>
@@ -1419,13 +1486,13 @@
         <v>15.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.774</v>
@@ -1434,16 +1501,16 @@
         <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U6" t="n">
         <v>22.9</v>
       </c>
       <c r="V6" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
@@ -1455,34 +1522,34 @@
         <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB6" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>12</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
         <v>13</v>
@@ -1497,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1515,7 +1582,7 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
@@ -1524,22 +1591,22 @@
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.304</v>
+        <v>0.308</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1598,16 +1665,16 @@
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0.759</v>
@@ -1622,7 +1689,7 @@
         <v>41</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V7" t="n">
         <v>14.1</v>
@@ -1643,13 +1710,13 @@
         <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ7" t="n">
         <v>4</v>
@@ -1673,13 +1740,13 @@
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM7" t="n">
         <v>16</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>13</v>
@@ -1697,13 +1764,13 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU7" t="n">
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -1712,16 +1779,16 @@
         <v>29</v>
       </c>
       <c r="AY7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA7" t="n">
         <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="n">
         <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>0.494</v>
+        <v>0.487</v>
       </c>
       <c r="H8" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I8" t="n">
         <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K8" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L8" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
         <v>19.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O8" t="n">
         <v>16.3</v>
@@ -1792,34 +1859,34 @@
         <v>20.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W8" t="n">
         <v>7.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y8" t="n">
         <v>4.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA8" t="n">
         <v>18.9</v>
@@ -1828,10 +1895,10 @@
         <v>101.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1843,13 +1910,13 @@
         <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>9</v>
@@ -1858,7 +1925,7 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
         <v>7</v>
@@ -1867,7 +1934,7 @@
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1879,10 +1946,10 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -1935,43 +2002,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
         <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I9" t="n">
         <v>40.6</v>
       </c>
       <c r="J9" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L9" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M9" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N9" t="n">
         <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0.697</v>
@@ -1986,13 +2053,13 @@
         <v>44.8</v>
       </c>
       <c r="U9" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V9" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>6.5</v>
@@ -2001,7 +2068,7 @@
         <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
         <v>21.7</v>
@@ -2010,10 +2077,10 @@
         <v>105.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2076,7 +2143,7 @@
         <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2184,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.35</v>
+        <v>0.342</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
         <v>17.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="O10" t="n">
         <v>15.8</v>
@@ -2156,7 +2223,7 @@
         <v>22.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="R10" t="n">
         <v>12.1</v>
@@ -2165,16 +2232,16 @@
         <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U10" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X10" t="n">
         <v>4.9</v>
@@ -2189,16 +2256,16 @@
         <v>19.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.1</v>
+        <v>-4.4</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
         <v>25</v>
@@ -2207,49 +2274,49 @@
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
         <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
         <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.457</v>
@@ -2326,34 +2393,34 @@
         <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
         <v>0.402</v>
       </c>
       <c r="O11" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0.79</v>
       </c>
       <c r="R11" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T11" t="n">
         <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W11" t="n">
         <v>6.9</v>
@@ -2365,13 +2432,13 @@
         <v>4.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AA11" t="n">
         <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0.7</v>
@@ -2389,10 +2456,10 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2419,7 +2486,7 @@
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2431,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2440,10 +2507,10 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2452,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -2481,37 +2548,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
         <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L12" t="n">
         <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
         <v>19.3</v>
@@ -2520,25 +2587,25 @@
         <v>25.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X12" t="n">
         <v>4.2</v>
@@ -2547,19 +2614,19 @@
         <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.8</v>
+        <v>106.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2574,22 +2641,22 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2607,16 +2674,16 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2625,13 +2692,13 @@
         <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>9</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" t="n">
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>0.62</v>
+        <v>0.628</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J13" t="n">
         <v>80.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
@@ -2693,34 +2760,34 @@
         <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O13" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P13" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R13" t="n">
         <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="U13" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V13" t="n">
         <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
         <v>6.4</v>
@@ -2735,13 +2802,13 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2762,7 +2829,7 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
         <v>16</v>
@@ -2774,7 +2841,7 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP13" t="n">
         <v>8</v>
@@ -2786,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
         <v>23</v>
@@ -2813,7 +2880,7 @@
         <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
@@ -2875,16 +2942,16 @@
         <v>21.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="O14" t="n">
         <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.711</v>
+        <v>0.712</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
@@ -2896,25 +2963,25 @@
         <v>41.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
         <v>14.7</v>
       </c>
       <c r="W14" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB14" t="n">
         <v>101.2</v>
@@ -2923,7 +2990,7 @@
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2947,13 +3014,13 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>16</v>
@@ -2965,7 +3032,7 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
         <v>21</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,10 +3056,10 @@
         <v>4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
         <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.538</v>
+        <v>0.532</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>80.8</v>
+        <v>81</v>
       </c>
       <c r="K15" t="n">
         <v>0.46</v>
@@ -3054,28 +3121,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S15" t="n">
         <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U15" t="n">
         <v>22.2</v>
@@ -3096,10 +3163,10 @@
         <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="AC15" t="n">
         <v>1.1</v>
@@ -3108,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -3120,22 +3187,22 @@
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
         <v>4</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
       <c r="L16" t="n">
         <v>4.6</v>
@@ -3239,16 +3306,16 @@
         <v>13.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P16" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
         <v>12.8</v>
@@ -3257,13 +3324,13 @@
         <v>29.6</v>
       </c>
       <c r="T16" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U16" t="n">
         <v>20.9</v>
       </c>
       <c r="V16" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W16" t="n">
         <v>8.6</v>
@@ -3281,28 +3348,28 @@
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC16" t="n">
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
         <v>18</v>
@@ -3320,13 +3387,13 @@
         <v>24</v>
       </c>
       <c r="AO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
         <v>4</v>
@@ -3341,7 +3408,7 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
@@ -3353,10 +3420,10 @@
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,28 +3476,28 @@
         <v>38.4</v>
       </c>
       <c r="J17" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.495</v>
+        <v>0.494</v>
       </c>
       <c r="L17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.395</v>
+        <v>0.394</v>
       </c>
       <c r="O17" t="n">
         <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R17" t="n">
         <v>8.300000000000001</v>
@@ -3454,22 +3521,22 @@
         <v>5.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.9</v>
+        <v>102.8</v>
       </c>
       <c r="AC17" t="n">
         <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3481,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
         <v>5</v>
@@ -3505,7 +3572,7 @@
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3514,13 +3581,13 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" t="n">
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.468</v>
+        <v>0.474</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,25 +3658,25 @@
         <v>38.2</v>
       </c>
       <c r="J18" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0.436</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O18" t="n">
         <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0.738</v>
@@ -3618,7 +3685,7 @@
         <v>13</v>
       </c>
       <c r="S18" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T18" t="n">
         <v>43.9</v>
@@ -3627,10 +3694,10 @@
         <v>22.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
         <v>6.8</v>
@@ -3642,16 +3709,16 @@
         <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB18" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
@@ -3672,25 +3739,25 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>14</v>
       </c>
       <c r="AM18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>2</v>
@@ -3708,13 +3775,13 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" t="n">
         <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>0.367</v>
+        <v>0.372</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3782,10 +3849,10 @@
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.304</v>
+        <v>0.303</v>
       </c>
       <c r="O19" t="n">
         <v>18.6</v>
@@ -3794,22 +3861,22 @@
         <v>25.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R19" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T19" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U19" t="n">
         <v>22.4</v>
       </c>
       <c r="V19" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W19" t="n">
         <v>8.4</v>
@@ -3827,13 +3894,13 @@
         <v>22.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
@@ -3872,16 +3939,16 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
         <v>15</v>
@@ -3890,16 +3957,16 @@
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
         <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>0.338</v>
+        <v>0.342</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J20" t="n">
         <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L20" t="n">
         <v>6.5</v>
@@ -3967,25 +4034,25 @@
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O20" t="n">
         <v>15.4</v>
       </c>
       <c r="P20" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.776</v>
+        <v>0.781</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>29.6</v>
       </c>
       <c r="T20" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U20" t="n">
         <v>21.1</v>
@@ -3997,16 +4064,16 @@
         <v>6.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB20" t="n">
         <v>94.2</v>
@@ -4018,16 +4085,16 @@
         <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4048,13 +4115,13 @@
         <v>12</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR20" t="n">
         <v>11</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
         <v>23</v>
@@ -4075,13 +4142,13 @@
         <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -4119,46 +4186,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F21" t="n">
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.658</v>
+        <v>0.654</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J21" t="n">
         <v>81.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
         <v>0.376</v>
       </c>
       <c r="O21" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P21" t="n">
         <v>21.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
@@ -4188,7 +4255,7 @@
         <v>20.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
         <v>100.2</v>
@@ -4197,7 +4264,7 @@
         <v>4.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
@@ -4212,19 +4279,19 @@
         <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="n">
         <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
         <v>5</v>
@@ -4263,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,10 +4386,10 @@
         <v>38.1</v>
       </c>
       <c r="J22" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="L22" t="n">
         <v>7.4</v>
@@ -4334,10 +4401,10 @@
         <v>0.382</v>
       </c>
       <c r="O22" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.829</v>
@@ -4352,7 +4419,7 @@
         <v>43.6</v>
       </c>
       <c r="U22" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
         <v>15.4</v>
@@ -4370,13 +4437,13 @@
         <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4394,7 +4461,7 @@
         <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4448,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>3</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>21</v>
@@ -4612,7 +4679,7 @@
         <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
         <v>11</v>
@@ -4621,13 +4688,13 @@
         <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
         <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>47</v>
       </c>
       <c r="G24" t="n">
-        <v>0.405</v>
+        <v>0.397</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,7 +4750,7 @@
         <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.443</v>
@@ -4695,34 +4762,34 @@
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
         <v>12.3</v>
       </c>
       <c r="P24" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X24" t="n">
         <v>4.6</v>
@@ -4731,7 +4798,7 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
         <v>16.3</v>
@@ -4740,10 +4807,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4758,7 +4825,7 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
@@ -4767,13 +4834,13 @@
         <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4806,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -4925,25 +4992,25 @@
         <v>-6.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
         <v>23</v>
@@ -4961,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4997,7 +5064,7 @@
         <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>0.418</v>
+        <v>0.423</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,7 +5114,7 @@
         <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
@@ -5059,7 +5126,7 @@
         <v>23.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
@@ -5068,7 +5135,7 @@
         <v>20.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5086,13 +5153,13 @@
         <v>14.6</v>
       </c>
       <c r="W26" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z26" t="n">
         <v>18.6</v>
@@ -5101,13 +5168,13 @@
         <v>18.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5125,10 +5192,10 @@
         <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5146,16 +5213,16 @@
         <v>24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>18</v>
@@ -5167,7 +5234,7 @@
         <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" t="n">
         <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,7 +5296,7 @@
         <v>37.6</v>
       </c>
       <c r="J27" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K27" t="n">
         <v>0.448</v>
@@ -5241,46 +5308,46 @@
         <v>20.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.366</v>
+        <v>0.363</v>
       </c>
       <c r="O27" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
         <v>0.771</v>
       </c>
       <c r="R27" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S27" t="n">
         <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V27" t="n">
         <v>14.7</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X27" t="n">
         <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
         <v>100.2</v>
@@ -5289,7 +5356,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5310,19 +5377,19 @@
         <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>11</v>
       </c>
       <c r="AM27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
@@ -5346,19 +5413,19 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
         <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.734</v>
+        <v>0.731</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,13 +5478,13 @@
         <v>39.2</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>21.6</v>
@@ -5432,13 +5499,13 @@
         <v>21.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T28" t="n">
         <v>41.3</v>
@@ -5453,7 +5520,7 @@
         <v>8.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.9</v>
@@ -5465,13 +5532,13 @@
         <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC28" t="n">
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5507,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>3</v>
@@ -5516,25 +5583,25 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
         <v>48</v>
       </c>
       <c r="G29" t="n">
-        <v>0.392</v>
+        <v>0.385</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K29" t="n">
         <v>0.444</v>
@@ -5602,16 +5669,16 @@
         <v>6.9</v>
       </c>
       <c r="M29" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N29" t="n">
         <v>0.339</v>
       </c>
       <c r="O29" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P29" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q29" t="n">
         <v>0.787</v>
@@ -5623,7 +5690,7 @@
         <v>29.3</v>
       </c>
       <c r="T29" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
         <v>21.5</v>
@@ -5635,13 +5702,13 @@
         <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA29" t="n">
         <v>20.1</v>
@@ -5650,10 +5717,10 @@
         <v>96.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5668,10 +5735,10 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
         <v>21</v>
@@ -5680,7 +5747,7 @@
         <v>15</v>
       </c>
       <c r="AM29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN29" t="n">
         <v>26</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5713,16 +5780,16 @@
         <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" t="n">
         <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.525</v>
+        <v>0.519</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,37 +5842,37 @@
         <v>37.3</v>
       </c>
       <c r="J30" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M30" t="n">
         <v>17.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
         <v>17.5</v>
       </c>
       <c r="P30" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R30" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
         <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U30" t="n">
         <v>22.8</v>
@@ -5817,22 +5884,22 @@
         <v>8.4</v>
       </c>
       <c r="X30" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA30" t="n">
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5853,19 +5920,19 @@
         <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK30" t="n">
         <v>12</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>10</v>
@@ -5874,7 +5941,7 @@
         <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5883,16 +5950,16 @@
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV30" t="n">
         <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5901,7 +5968,7 @@
         <v>23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5969,22 +6036,22 @@
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
         <v>21.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T31" t="n">
         <v>43.2</v>
@@ -5999,22 +6066,22 @@
         <v>7.3</v>
       </c>
       <c r="X31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y31" t="n">
         <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD31" t="n">
         <v>1</v>
@@ -6035,19 +6102,19 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO31" t="n">
         <v>24</v>
@@ -6071,19 +6138,19 @@
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>23</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-12-2012-13</t>
+          <t>2013-04-12</t>
         </is>
       </c>
     </row>
